--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -4185,34 +4185,34 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>5396100</v>
+        <v>6386000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>26322</v>
+        <v>31151</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>5396100</v>
+        <v>5396170</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>26322</v>
+        <v>26323</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18795,12 +18795,12 @@
 (21年-04月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
-$540万
-$26,322/呎
-(26年-09月-02日)</t>
+$639万
+$31,151/呎
+(在售)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -891,38 +891,30 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>13667500</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>38500</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K5" s="5" t="n">
+        <v>13667500</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>38500</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -931,7 +923,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18244,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18262,7 +18254,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18394,12 +18386,12 @@
 (21年-06月-24日)</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 355呎 (2房)
-招标单位
--
-(在售)</t>
+$1367万
+$38,500/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -18375,7 +18375,7 @@
           <t>D | 419呎 (2房)
 $1522万
 $36,313/呎
-(26年-08月-27日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -4177,34 +4177,34 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>6386000</v>
+        <v>5396100</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>31151</v>
+        <v>26322</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>5396170</v>
+        <v>5396100</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>26323</v>
+        <v>26322</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18787,12 +18787,12 @@
 (21年-04月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
-$639万
-$31,151/呎
-(在售)</t>
+$540万
+$26,322/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -18391,7 +18391,7 @@
           <t>F | 355呎 (2房)
 $1367万
 $38,500/呎
-(26年-09月-10日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -264,10 +264,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -821,38 +821,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>13135000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>37000</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="5" t="n">
+        <v>13135000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>37000</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -861,7 +853,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18236,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18254,7 +18246,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18394,12 +18386,12 @@
 (26年-10月-06日)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 355呎 (2房)
-招标单位
--
-(在售)</t>
+$1314万
+$37,000/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -18410,11 +18402,11 @@
 (21年-06月-25日)</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr"/>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+      <c r="M5" s="21" t="inlineStr"/>
+      <c r="N5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -18454,7 +18446,7 @@
 (21年-01月-15日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $694万
@@ -18565,7 +18557,7 @@
 (21年-02月-08日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $682万
@@ -18676,7 +18668,7 @@
 (21年-02月-08日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $643万
@@ -18898,7 +18890,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $634万

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -18391,7 +18391,7 @@
           <t>G | 355呎 (2房)
 $1314万
 $37,000/呎
-(26年-10月-09日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -18784,7 +18784,7 @@
           <t>E | 205呎 (开放式)
 $540万
 $26,322/呎
-(26年-10月-03日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">

--- a/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
+++ b/港岛-北角-君誉峰/君誉峰_销控明细表.xlsx
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>15215200</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>36313</v>
+        <v>36400</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>15215200</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>36313</v>
+        <v>36400</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>19280000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>46014</v>
+        <v>46124</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>19280000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>46014</v>
+        <v>46124</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>8227540</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>28667</v>
+        <v>28568</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>8227540</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>28667</v>
+        <v>28568</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>7833720</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>27295</v>
+        <v>27200</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>7833720</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>27295</v>
+        <v>27200</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>7757090</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>27028</v>
+        <v>26934</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>7757090</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>27028</v>
+        <v>26934</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>7700160</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>26830</v>
+        <v>26737</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>7700160</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>26830</v>
+        <v>26737</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>7625280</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>26569</v>
+        <v>26477</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>7625280</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>26569</v>
+        <v>26477</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>7573440</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>26388</v>
+        <v>26297</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>7573440</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>26388</v>
+        <v>26297</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>7338240</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>25569</v>
+        <v>25480</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>7338240</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>25569</v>
+        <v>25480</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>7385580</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>25734</v>
+        <v>25644</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>7385580</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>25734</v>
+        <v>25644</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>7182720</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>25027</v>
+        <v>24940</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>7182720</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>25027</v>
+        <v>24940</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>7104000</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>24753</v>
+        <v>24667</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>7104000</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>24753</v>
+        <v>24667</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>7023360</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>24472</v>
+        <v>24387</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>7023360</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>24472</v>
+        <v>24387</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>7052160</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>24572</v>
+        <v>24487</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>7052160</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>24572</v>
+        <v>24487</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="E269" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>6974400</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>24301</v>
+        <v>24217</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>6974400</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>24301</v>
+        <v>24217</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="E277" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>8339520</v>
       </c>
       <c r="I277" s="5" t="n">
-        <v>29058</v>
+        <v>28957</v>
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>8339520</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>29058</v>
+        <v>28957</v>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>8342400</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>29068</v>
+        <v>28967</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>8342400</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>29068</v>
+        <v>28967</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -18340,9 +18340,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 419呎 (2房)
+          <t>A | 418呎 (2房)
 $1928万
-$46,014/呎
+$46,124/呎
 (22年-01月-27日)</t>
         </is>
       </c>
@@ -18364,9 +18364,9 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 419呎 (2房)
+          <t>D | 418呎 (2房)
 $1522万
-$36,313/呎
+$36,400/呎
 (26年-09月-21日)</t>
         </is>
       </c>
@@ -18464,9 +18464,9 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>G | 287呎 (1房)
+          <t>G | 288呎 (1房)
 $823万
-$28,667/呎
+$28,568/呎
 (21年-03月-08日)</t>
         </is>
       </c>
@@ -19090,9 +19090,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $776万
-$27,028/呎
+$26,934/呎
 (21年-05月-15日)</t>
         </is>
       </c>
@@ -19130,9 +19130,9 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>G | 287呎 (1房)
+          <t>G | 288呎 (1房)
 $783万
-$27,295/呎
+$27,200/呎
 (21年-01月-20日)</t>
         </is>
       </c>
@@ -19201,9 +19201,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $763万
-$26,569/呎
+$26,477/呎
 (21年-05月-05日)</t>
         </is>
       </c>
@@ -19241,9 +19241,9 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>G | 287呎 (1房)
+          <t>G | 288呎 (1房)
 $770万
-$26,830/呎
+$26,737/呎
 (21年-02月-04日)</t>
         </is>
       </c>
@@ -19312,9 +19312,9 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $757万
-$26,388/呎
+$26,297/呎
 (21年-03月-17日)</t>
         </is>
       </c>
@@ -19756,9 +19756,9 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $734万
-$25,569/呎
+$25,480/呎
 (21年-05月-13日)</t>
         </is>
       </c>
@@ -19907,9 +19907,9 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>G | 287呎 (1房)
+          <t>G | 288呎 (1房)
 $739万
-$25,734/呎
+$25,644/呎
 (20年-12月-23日)</t>
         </is>
       </c>
@@ -20089,9 +20089,9 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $718万
-$25,027/呎
+$24,940/呎
 (21年-03月-17日)</t>
         </is>
       </c>
@@ -20311,9 +20311,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $710万
-$24,753/呎
+$24,667/呎
 (21年-04月-01日)</t>
         </is>
       </c>
@@ -20422,9 +20422,9 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $705万
-$24,572/呎
+$24,487/呎
 (21年-04月-14日)</t>
         </is>
       </c>
@@ -20462,9 +20462,9 @@
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>G | 287呎 (1房)
+          <t>G | 288呎 (1房)
 $702万
-$24,472/呎
+$24,387/呎
 (20年-12月-23日)</t>
         </is>
       </c>
@@ -20533,9 +20533,9 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $697万
-$24,301/呎
+$24,217/呎
 (21年-02月-25日)</t>
         </is>
       </c>
@@ -20644,9 +20644,9 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 287呎 (1房)
+          <t>B | 288呎 (1房)
 $834万
-$29,068/呎
+$28,967/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -20684,9 +20684,9 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>G | 287呎 (1房)
+          <t>G | 288呎 (1房)
 $834万
-$29,058/呎
+$28,957/呎
 (21年-12月-14日)</t>
         </is>
       </c>
